--- a/academias/Química - Estadisticos 20211.xlsx
+++ b/academias/Química - Estadisticos 20211.xlsx
@@ -504,25 +504,25 @@
         <v>40</v>
       </c>
       <c r="E2">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="F2">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>57.5</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>42.5</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>8.1</v>
+        <v>7.3</v>
       </c>
       <c r="J2">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>42.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -539,25 +539,25 @@
         <v>44</v>
       </c>
       <c r="E3">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>68.18000000000001</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>31.82</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="J3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>31.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -574,25 +574,25 @@
         <v>43</v>
       </c>
       <c r="E4">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="F4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>81.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>18.6</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>18.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -609,25 +609,25 @@
         <v>28</v>
       </c>
       <c r="E5">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>64.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>35.71</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>35.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -644,25 +644,25 @@
         <v>21</v>
       </c>
       <c r="E6">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>71.43000000000001</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>28.57</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>8.300000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="J6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>28.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -679,25 +679,25 @@
         <v>34</v>
       </c>
       <c r="E7">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F7">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G7">
-        <v>82.34999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="H7">
-        <v>17.65</v>
+        <v>5.88</v>
       </c>
       <c r="I7">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="J7">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K7">
-        <v>17.65</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -784,25 +784,25 @@
         <v>43</v>
       </c>
       <c r="E10">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F10">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G10">
-        <v>74.42</v>
+        <v>83.72</v>
       </c>
       <c r="H10">
-        <v>25.58</v>
+        <v>16.28</v>
       </c>
       <c r="I10">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J10">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="K10">
-        <v>25.58</v>
+        <v>16.28</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -819,25 +819,25 @@
         <v>43</v>
       </c>
       <c r="E11">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F11">
+        <v>6</v>
+      </c>
+      <c r="G11">
+        <v>86.05</v>
+      </c>
+      <c r="H11">
+        <v>13.95</v>
+      </c>
+      <c r="I11">
         <v>8</v>
       </c>
-      <c r="G11">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="H11">
-        <v>18.6</v>
-      </c>
-      <c r="I11">
-        <v>8.1</v>
-      </c>
       <c r="J11">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K11">
-        <v>18.6</v>
+        <v>13.95</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -854,25 +854,25 @@
         <v>24</v>
       </c>
       <c r="E12">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G12">
-        <v>83.33</v>
+        <v>95.83</v>
       </c>
       <c r="H12">
-        <v>16.67</v>
+        <v>4.17</v>
       </c>
       <c r="I12">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="J12">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K12">
-        <v>16.67</v>
+        <v>4.17</v>
       </c>
     </row>
   </sheetData>
@@ -938,22 +938,25 @@
         <v>40</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>7.6</v>
       </c>
       <c r="J2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -970,22 +973,25 @@
         <v>44</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F3">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>8.1</v>
       </c>
       <c r="J3">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1002,22 +1008,25 @@
         <v>43</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="F4">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>8.199999999999999</v>
       </c>
       <c r="J4">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1034,22 +1043,25 @@
         <v>28</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F5">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>7.7</v>
       </c>
       <c r="J5">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1066,22 +1078,25 @@
         <v>21</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F6">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1098,22 +1113,25 @@
         <v>34</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F7">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H7">
-        <v>100</v>
+        <v>14.71</v>
+      </c>
+      <c r="I7">
+        <v>8.4</v>
       </c>
       <c r="J7">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="K7">
-        <v>100</v>
+        <v>14.71</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1130,22 +1148,25 @@
         <v>31</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F8">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>64.52</v>
       </c>
       <c r="H8">
-        <v>100</v>
+        <v>35.48</v>
+      </c>
+      <c r="I8">
+        <v>8.1</v>
       </c>
       <c r="J8">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="K8">
-        <v>100</v>
+        <v>35.48</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1162,22 +1183,25 @@
         <v>36</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F9">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>77.78</v>
       </c>
       <c r="H9">
-        <v>100</v>
+        <v>22.22</v>
+      </c>
+      <c r="I9">
+        <v>8.6</v>
       </c>
       <c r="J9">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="K9">
-        <v>100</v>
+        <v>22.22</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1194,22 +1218,25 @@
         <v>43</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F10">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>72.09</v>
       </c>
       <c r="H10">
-        <v>100</v>
+        <v>27.91</v>
+      </c>
+      <c r="I10">
+        <v>8.699999999999999</v>
       </c>
       <c r="J10">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="K10">
-        <v>100</v>
+        <v>27.91</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1226,22 +1253,25 @@
         <v>43</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F11">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>83.72</v>
       </c>
       <c r="H11">
-        <v>100</v>
+        <v>16.28</v>
+      </c>
+      <c r="I11">
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="K11">
-        <v>100</v>
+        <v>16.28</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1258,22 +1288,25 @@
         <v>24</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F12">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>91.67</v>
       </c>
       <c r="H12">
-        <v>100</v>
+        <v>8.33</v>
+      </c>
+      <c r="I12">
+        <v>8.9</v>
       </c>
       <c r="J12">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="K12">
-        <v>100</v>
+        <v>8.33</v>
       </c>
     </row>
   </sheetData>
@@ -1339,25 +1372,25 @@
         <v>40</v>
       </c>
       <c r="E2">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="F2">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>57.5</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>42.5</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="J2">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>42.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1374,25 +1407,25 @@
         <v>44</v>
       </c>
       <c r="E3">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>68.18000000000001</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>31.82</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
       <c r="J3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>31.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1409,25 +1442,25 @@
         <v>43</v>
       </c>
       <c r="E4">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="F4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>81.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>18.6</v>
+        <v>0</v>
       </c>
       <c r="I4">
         <v>8.199999999999999</v>
       </c>
       <c r="J4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>18.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1444,25 +1477,25 @@
         <v>28</v>
       </c>
       <c r="E5">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>64.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>35.71</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>8.699999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>35.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1479,25 +1512,25 @@
         <v>21</v>
       </c>
       <c r="E6">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>71.43000000000001</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>28.57</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>28.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1514,25 +1547,25 @@
         <v>34</v>
       </c>
       <c r="E7">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F7">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G7">
-        <v>82.34999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="H7">
-        <v>17.65</v>
+        <v>5.88</v>
       </c>
       <c r="I7">
         <v>8.4</v>
       </c>
       <c r="J7">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K7">
-        <v>17.65</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1561,7 +1594,7 @@
         <v>25.81</v>
       </c>
       <c r="I8">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
       <c r="J8">
         <v>8</v>
@@ -1596,7 +1629,7 @@
         <v>8.33</v>
       </c>
       <c r="I9">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J9">
         <v>3</v>
@@ -1619,25 +1652,25 @@
         <v>43</v>
       </c>
       <c r="E10">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F10">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G10">
-        <v>74.42</v>
+        <v>83.72</v>
       </c>
       <c r="H10">
-        <v>25.58</v>
+        <v>16.28</v>
       </c>
       <c r="I10">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J10">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="K10">
-        <v>25.58</v>
+        <v>16.28</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1654,25 +1687,25 @@
         <v>43</v>
       </c>
       <c r="E11">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F11">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G11">
-        <v>81.40000000000001</v>
+        <v>86.05</v>
       </c>
       <c r="H11">
-        <v>18.6</v>
+        <v>13.95</v>
       </c>
       <c r="I11">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J11">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K11">
-        <v>18.6</v>
+        <v>13.95</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1689,25 +1722,25 @@
         <v>24</v>
       </c>
       <c r="E12">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G12">
-        <v>83.33</v>
+        <v>95.83</v>
       </c>
       <c r="H12">
-        <v>16.67</v>
+        <v>4.17</v>
       </c>
       <c r="I12">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J12">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K12">
-        <v>16.67</v>
+        <v>4.17</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Química - Estadisticos 20211.xlsx
+++ b/academias/Química - Estadisticos 20211.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="1er Parcial" sheetId="1" r:id="rId1"/>
     <sheet name="2o Parcial" sheetId="2" r:id="rId2"/>
-    <sheet name="3er Parcial" sheetId="3" r:id="rId3"/>
+    <sheet name="Final" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -97,6 +97,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -149,8 +153,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -451,42 +457,45 @@
   <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -509,19 +518,19 @@
       <c r="F2">
         <v>0</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>100</v>
       </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
+      <c r="H2" s="1">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2">
         <v>7.3</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>0</v>
       </c>
     </row>
@@ -544,19 +553,19 @@
       <c r="F3">
         <v>0</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>100</v>
       </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
+      <c r="H3" s="1">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2">
         <v>7.8</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>0</v>
       </c>
     </row>
@@ -579,19 +588,19 @@
       <c r="F4">
         <v>0</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>100</v>
       </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
+      <c r="H4" s="1">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
         <v>7.8</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>0</v>
       </c>
     </row>
@@ -614,19 +623,19 @@
       <c r="F5">
         <v>0</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>100</v>
       </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
+      <c r="H5" s="1">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2">
         <v>7.8</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>0</v>
       </c>
     </row>
@@ -649,19 +658,19 @@
       <c r="F6">
         <v>0</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>100</v>
       </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
         <v>7.6</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>0</v>
       </c>
     </row>
@@ -684,19 +693,19 @@
       <c r="F7">
         <v>2</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>94.12</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>5.88</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>8.1</v>
       </c>
       <c r="J7">
         <v>2</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>5.88</v>
       </c>
     </row>
@@ -719,19 +728,19 @@
       <c r="F8">
         <v>8</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>74.19</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>25.81</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>7.7</v>
       </c>
       <c r="J8">
         <v>8</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>25.81</v>
       </c>
     </row>
@@ -754,19 +763,19 @@
       <c r="F9">
         <v>3</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>91.67</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>8.33</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>8.6</v>
       </c>
       <c r="J9">
         <v>3</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>8.33</v>
       </c>
     </row>
@@ -789,19 +798,19 @@
       <c r="F10">
         <v>7</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>83.72</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>16.28</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="2">
         <v>8.199999999999999</v>
       </c>
       <c r="J10">
         <v>7</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>16.28</v>
       </c>
     </row>
@@ -824,19 +833,19 @@
       <c r="F11">
         <v>6</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>86.05</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>13.95</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="2">
         <v>8</v>
       </c>
       <c r="J11">
         <v>6</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>13.95</v>
       </c>
     </row>
@@ -859,19 +868,19 @@
       <c r="F12">
         <v>1</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>95.83</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>4.17</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="2">
         <v>8.5</v>
       </c>
       <c r="J12">
         <v>1</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>4.17</v>
       </c>
     </row>
@@ -885,42 +894,45 @@
   <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -943,19 +955,19 @@
       <c r="F2">
         <v>0</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>100</v>
       </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
+      <c r="H2" s="1">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2">
         <v>7.6</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>0</v>
       </c>
     </row>
@@ -978,19 +990,19 @@
       <c r="F3">
         <v>0</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>100</v>
       </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
+      <c r="H3" s="1">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2">
         <v>8.1</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1013,19 +1025,19 @@
       <c r="F4">
         <v>0</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>100</v>
       </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
+      <c r="H4" s="1">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
         <v>8.199999999999999</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1048,19 +1060,19 @@
       <c r="F5">
         <v>0</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>100</v>
       </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
+      <c r="H5" s="1">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2">
         <v>7.7</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1083,19 +1095,19 @@
       <c r="F6">
         <v>0</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>100</v>
       </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
         <v>8</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1118,19 +1130,19 @@
       <c r="F7">
         <v>5</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>85.29000000000001</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>14.71</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>8.4</v>
       </c>
       <c r="J7">
         <v>5</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>14.71</v>
       </c>
     </row>
@@ -1153,19 +1165,19 @@
       <c r="F8">
         <v>11</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>64.52</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>35.48</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>8.1</v>
       </c>
       <c r="J8">
         <v>11</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>35.48</v>
       </c>
     </row>
@@ -1188,19 +1200,19 @@
       <c r="F9">
         <v>8</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>77.78</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>22.22</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>8.6</v>
       </c>
       <c r="J9">
         <v>8</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>22.22</v>
       </c>
     </row>
@@ -1223,19 +1235,19 @@
       <c r="F10">
         <v>12</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>72.09</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>27.91</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="2">
         <v>8.699999999999999</v>
       </c>
       <c r="J10">
         <v>12</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>27.91</v>
       </c>
     </row>
@@ -1258,19 +1270,19 @@
       <c r="F11">
         <v>7</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>83.72</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>16.28</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="2">
         <v>8</v>
       </c>
       <c r="J11">
         <v>7</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>16.28</v>
       </c>
     </row>
@@ -1293,19 +1305,19 @@
       <c r="F12">
         <v>2</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>91.67</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>8.33</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="2">
         <v>8.9</v>
       </c>
       <c r="J12">
         <v>2</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>8.33</v>
       </c>
     </row>
@@ -1319,42 +1331,45 @@
   <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1377,19 +1392,19 @@
       <c r="F2">
         <v>0</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>100</v>
       </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
+      <c r="H2" s="1">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2">
         <v>7.7</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1412,19 +1427,19 @@
       <c r="F3">
         <v>0</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>100</v>
       </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
+      <c r="H3" s="1">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2">
         <v>8.1</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1447,19 +1462,19 @@
       <c r="F4">
         <v>0</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>100</v>
       </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
+      <c r="H4" s="1">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
         <v>8.199999999999999</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1482,19 +1497,19 @@
       <c r="F5">
         <v>0</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>100</v>
       </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
+      <c r="H5" s="1">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2">
         <v>7.9</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1517,19 +1532,19 @@
       <c r="F6">
         <v>0</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>100</v>
       </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
         <v>8</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1552,19 +1567,19 @@
       <c r="F7">
         <v>2</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>94.12</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>5.88</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>8.4</v>
       </c>
       <c r="J7">
         <v>2</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>5.88</v>
       </c>
     </row>
@@ -1587,19 +1602,19 @@
       <c r="F8">
         <v>8</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>74.19</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>25.81</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>8.1</v>
       </c>
       <c r="J8">
         <v>8</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>25.81</v>
       </c>
     </row>
@@ -1622,19 +1637,19 @@
       <c r="F9">
         <v>3</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>91.67</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>8.33</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>8.800000000000001</v>
       </c>
       <c r="J9">
         <v>3</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>8.33</v>
       </c>
     </row>
@@ -1657,19 +1672,19 @@
       <c r="F10">
         <v>7</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>83.72</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>16.28</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="2">
         <v>8.6</v>
       </c>
       <c r="J10">
         <v>7</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>16.28</v>
       </c>
     </row>
@@ -1692,19 +1707,19 @@
       <c r="F11">
         <v>6</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>86.05</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>13.95</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="2">
         <v>8.199999999999999</v>
       </c>
       <c r="J11">
         <v>6</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>13.95</v>
       </c>
     </row>
@@ -1727,19 +1742,19 @@
       <c r="F12">
         <v>1</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>95.83</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>4.17</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="2">
         <v>8.9</v>
       </c>
       <c r="J12">
         <v>1</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>4.17</v>
       </c>
     </row>

--- a/academias/Química - Estadisticos 20211.xlsx
+++ b/academias/Química - Estadisticos 20211.xlsx
@@ -98,7 +98,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="0.0\%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="2">

--- a/academias/Química - Estadisticos 20211.xlsx
+++ b/academias/Química - Estadisticos 20211.xlsx
@@ -688,25 +688,25 @@
         <v>34</v>
       </c>
       <c r="E7">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>94.12</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
-        <v>5.88</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>5.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -723,25 +723,25 @@
         <v>31</v>
       </c>
       <c r="E8">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F8">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G8" s="1">
-        <v>74.19</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="H8" s="1">
-        <v>25.81</v>
+        <v>9.68</v>
       </c>
       <c r="I8" s="2">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="J8">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>25.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -758,25 +758,25 @@
         <v>36</v>
       </c>
       <c r="E9">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>91.67</v>
+        <v>100</v>
       </c>
       <c r="H9" s="1">
-        <v>8.33</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>8.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -793,25 +793,25 @@
         <v>43</v>
       </c>
       <c r="E10">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F10">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G10" s="1">
-        <v>83.72</v>
+        <v>90.7</v>
       </c>
       <c r="H10" s="1">
-        <v>16.28</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I10" s="2">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J10">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>16.28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -828,25 +828,25 @@
         <v>43</v>
       </c>
       <c r="E11">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G11" s="1">
-        <v>86.05</v>
+        <v>88.37</v>
       </c>
       <c r="H11" s="1">
-        <v>13.95</v>
+        <v>11.63</v>
       </c>
       <c r="I11" s="2">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="J11">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>13.95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -863,25 +863,25 @@
         <v>24</v>
       </c>
       <c r="E12">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>95.83</v>
+        <v>100</v>
       </c>
       <c r="H12" s="1">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
         <v>8.5</v>
       </c>
       <c r="J12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1125,25 +1125,25 @@
         <v>34</v>
       </c>
       <c r="E7">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>85.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
-        <v>14.71</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="J7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>14.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1160,25 +1160,25 @@
         <v>31</v>
       </c>
       <c r="E8">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F8">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G8" s="1">
-        <v>64.52</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="H8" s="1">
-        <v>35.48</v>
+        <v>9.68</v>
       </c>
       <c r="I8" s="2">
-        <v>8.1</v>
+        <v>7.3</v>
       </c>
       <c r="J8">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>35.48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1195,25 +1195,25 @@
         <v>36</v>
       </c>
       <c r="E9">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F9">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>77.78</v>
+        <v>100</v>
       </c>
       <c r="H9" s="1">
-        <v>22.22</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J9">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>22.22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1230,25 +1230,25 @@
         <v>43</v>
       </c>
       <c r="E10">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F10">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G10" s="1">
-        <v>72.09</v>
+        <v>88.37</v>
       </c>
       <c r="H10" s="1">
-        <v>27.91</v>
+        <v>11.63</v>
       </c>
       <c r="I10" s="2">
-        <v>8.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="J10">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>27.91</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1265,25 +1265,25 @@
         <v>43</v>
       </c>
       <c r="E11">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G11" s="1">
-        <v>83.72</v>
+        <v>88.37</v>
       </c>
       <c r="H11" s="1">
-        <v>16.28</v>
+        <v>11.63</v>
       </c>
       <c r="I11" s="2">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="J11">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>16.28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1300,25 +1300,25 @@
         <v>24</v>
       </c>
       <c r="E12">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>91.67</v>
+        <v>100</v>
       </c>
       <c r="H12" s="1">
-        <v>8.33</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="J12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>8.33</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1399,7 +1399,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1434,7 +1434,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1469,7 +1469,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1504,7 +1504,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>7.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1562,25 +1562,25 @@
         <v>34</v>
       </c>
       <c r="E7">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>94.12</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
-        <v>5.88</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>8.4</v>
+        <v>7.9</v>
       </c>
       <c r="J7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>5.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1597,25 +1597,25 @@
         <v>31</v>
       </c>
       <c r="E8">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F8">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G8" s="1">
-        <v>74.19</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="H8" s="1">
-        <v>25.81</v>
+        <v>9.68</v>
       </c>
       <c r="I8" s="2">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
       <c r="J8">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>25.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1632,25 +1632,25 @@
         <v>36</v>
       </c>
       <c r="E9">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>91.67</v>
+        <v>100</v>
       </c>
       <c r="H9" s="1">
-        <v>8.33</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>8.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1667,25 +1667,25 @@
         <v>43</v>
       </c>
       <c r="E10">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F10">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G10" s="1">
-        <v>83.72</v>
+        <v>88.37</v>
       </c>
       <c r="H10" s="1">
-        <v>16.28</v>
+        <v>11.63</v>
       </c>
       <c r="I10" s="2">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="J10">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>16.28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1714,13 +1714,13 @@
         <v>13.95</v>
       </c>
       <c r="I11" s="2">
-        <v>8.199999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="J11">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>13.95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1737,25 +1737,25 @@
         <v>24</v>
       </c>
       <c r="E12">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>95.83</v>
+        <v>100</v>
       </c>
       <c r="H12" s="1">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>8.9</v>
+        <v>8.1</v>
       </c>
       <c r="J12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>4.17</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
